--- a/output/Data and Chart Outputs/argentina_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/argentina_power_capacity.xlsx
@@ -843,7 +843,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAMMESA publishes thermal capacity by machine type, not fuel: Gas_MW = Ciclos Combinados + Turbina a gas + Turbovapor (natural-gas plants; most can also burn gasoil or fuel oil); Oil_MW = Motor Diesel (gasoil/fuel oil engines); Coal_MW = the Rio Turbio coal-fired steam units, taken out of Turbovapor by plant name.</t>
+          <t>CAMMESA publishes thermal capacity by machine type, not fuel: Gas_MW = Ciclos Combinados + Turbina a gas + Turbovapor (natural-gas plants; most can also burn gasoil or fuel oil); Oil_MW = Motor Diesel (gasoil/fuel oil engines). Coal_MW would take the Rio Turbio coal plant out of Turbovapor by name, but Rio Turbio is not in CAMMESA's machine list, so Coal_MW is 0; steam units able to burn coal (e.g. San Nicolas) stay in Gas_MW because CAMMESA does not split steam turbines by fuel.</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/argentina_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/argentina_power_capacity.xlsx
@@ -368,6 +368,34 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$69</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$69</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -456,7 +484,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -880,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -914,17 +942,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Bioenergy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Bioenergy</t>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nuclear &amp; other</t>
         </is>
       </c>
     </row>
@@ -945,13 +978,16 @@
         <v>0.766</v>
       </c>
       <c r="F2" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.646</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.1102</v>
       </c>
     </row>
     <row r="3">
@@ -971,13 +1007,16 @@
         <v>0.766</v>
       </c>
       <c r="F3" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.646</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1202</v>
       </c>
     </row>
     <row r="4">
@@ -997,13 +1036,16 @@
         <v>0.766</v>
       </c>
       <c r="F4" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.646</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.1222</v>
       </c>
     </row>
     <row r="5">
@@ -1023,13 +1065,16 @@
         <v>0.769</v>
       </c>
       <c r="F5" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.646</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.1222</v>
       </c>
     </row>
     <row r="6">
@@ -1049,13 +1094,16 @@
         <v>0.769</v>
       </c>
       <c r="F6" t="n">
+        <v>1.6424</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.6424</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1222</v>
       </c>
     </row>
     <row r="7">
@@ -1075,13 +1123,16 @@
         <v>0.769</v>
       </c>
       <c r="F7" t="n">
+        <v>1.6424</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.6424</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.1303</v>
       </c>
     </row>
     <row r="8">
@@ -1101,13 +1152,16 @@
         <v>0.869</v>
       </c>
       <c r="F8" t="n">
+        <v>1.6424</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.6424</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.1326</v>
       </c>
     </row>
     <row r="9">
@@ -1127,13 +1181,16 @@
         <v>0.869</v>
       </c>
       <c r="F9" t="n">
+        <v>1.6574</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.6574</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1326</v>
       </c>
     </row>
     <row r="10">
@@ -1153,13 +1210,16 @@
         <v>0.869</v>
       </c>
       <c r="F10" t="n">
+        <v>1.6574</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.6574</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.1326</v>
       </c>
     </row>
     <row r="11">
@@ -1179,13 +1239,16 @@
         <v>1.069</v>
       </c>
       <c r="F11" t="n">
+        <v>1.6574</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.6574</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.1326</v>
       </c>
     </row>
     <row r="12">
@@ -1205,13 +1268,16 @@
         <v>1.069</v>
       </c>
       <c r="F12" t="n">
+        <v>1.6574</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.6574</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="13">
@@ -1231,13 +1297,16 @@
         <v>1.0602</v>
       </c>
       <c r="F13" t="n">
+        <v>1.6878</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.6878</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="14">
@@ -1257,13 +1326,16 @@
         <v>1.0602</v>
       </c>
       <c r="F14" t="n">
+        <v>1.6878</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.6878</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="15">
@@ -1283,13 +1355,16 @@
         <v>1.0602</v>
       </c>
       <c r="F15" t="n">
+        <v>1.6878</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.6878</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="16">
@@ -1309,13 +1384,16 @@
         <v>1.0652</v>
       </c>
       <c r="F16" t="n">
+        <v>1.6878</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.6878</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="17">
@@ -1335,13 +1413,16 @@
         <v>1.0652</v>
       </c>
       <c r="F17" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="18">
@@ -1361,13 +1442,16 @@
         <v>1.0752</v>
       </c>
       <c r="F18" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="19">
@@ -1387,13 +1471,16 @@
         <v>1.0752</v>
       </c>
       <c r="F19" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1393</v>
       </c>
     </row>
     <row r="20">
@@ -1413,13 +1500,16 @@
         <v>1.0752</v>
       </c>
       <c r="F20" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1417</v>
       </c>
     </row>
     <row r="21">
@@ -1439,13 +1529,16 @@
         <v>1.0752</v>
       </c>
       <c r="F21" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1429</v>
       </c>
     </row>
     <row r="22">
@@ -1465,13 +1558,16 @@
         <v>1.0752</v>
       </c>
       <c r="F22" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1429</v>
       </c>
     </row>
     <row r="23">
@@ -1491,13 +1587,16 @@
         <v>1.0752</v>
       </c>
       <c r="F23" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1429</v>
       </c>
     </row>
     <row r="24">
@@ -1517,13 +1616,16 @@
         <v>1.0852</v>
       </c>
       <c r="F24" t="n">
+        <v>1.6733</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.6733</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1429</v>
       </c>
     </row>
     <row r="25">
@@ -1543,13 +1645,16 @@
         <v>1.0858</v>
       </c>
       <c r="F25" t="n">
+        <v>1.6964</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.6964</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1429</v>
       </c>
     </row>
     <row r="26">
@@ -1569,13 +1674,16 @@
         <v>1.0858</v>
       </c>
       <c r="F26" t="n">
+        <v>1.6964</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.6964</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1429</v>
       </c>
     </row>
     <row r="27">
@@ -1595,13 +1703,16 @@
         <v>1.0908</v>
       </c>
       <c r="F27" t="n">
+        <v>1.6964</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.6964</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1449</v>
       </c>
     </row>
     <row r="28">
@@ -1621,13 +1732,16 @@
         <v>1.1688</v>
       </c>
       <c r="F28" t="n">
+        <v>1.6904</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.6904</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1449</v>
       </c>
     </row>
     <row r="29">
@@ -1647,13 +1761,16 @@
         <v>1.1938</v>
       </c>
       <c r="F29" t="n">
+        <v>1.6904</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.6904</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1449</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1790,16 @@
         <v>1.2938</v>
       </c>
       <c r="F30" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.1481</v>
       </c>
     </row>
     <row r="31">
@@ -1699,13 +1819,16 @@
         <v>1.3158</v>
       </c>
       <c r="F31" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.1481</v>
       </c>
     </row>
     <row r="32">
@@ -1725,13 +1848,16 @@
         <v>1.3158</v>
       </c>
       <c r="F32" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.1531</v>
       </c>
     </row>
     <row r="33">
@@ -1751,13 +1877,16 @@
         <v>1.3158</v>
       </c>
       <c r="F33" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.1531</v>
       </c>
     </row>
     <row r="34">
@@ -1777,13 +1906,16 @@
         <v>1.3158</v>
       </c>
       <c r="F34" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.1531</v>
       </c>
     </row>
     <row r="35">
@@ -1803,13 +1935,16 @@
         <v>1.3158</v>
       </c>
       <c r="F35" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.1531</v>
       </c>
     </row>
     <row r="36">
@@ -1829,13 +1964,16 @@
         <v>1.3158</v>
       </c>
       <c r="F36" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.6584</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.1545</v>
       </c>
     </row>
     <row r="37">
@@ -1855,13 +1993,16 @@
         <v>1.3659</v>
       </c>
       <c r="F37" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.1514</v>
       </c>
     </row>
     <row r="38">
@@ -1881,13 +2022,16 @@
         <v>1.3879</v>
       </c>
       <c r="F38" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.1514</v>
       </c>
     </row>
     <row r="39">
@@ -1907,13 +2051,16 @@
         <v>1.3931</v>
       </c>
       <c r="F39" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.1514</v>
       </c>
     </row>
     <row r="40">
@@ -1933,13 +2080,16 @@
         <v>1.3931</v>
       </c>
       <c r="F40" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.1514</v>
       </c>
     </row>
     <row r="41">
@@ -1959,13 +2109,16 @@
         <v>1.4003</v>
       </c>
       <c r="F41" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.1514</v>
       </c>
     </row>
     <row r="42">
@@ -1985,13 +2138,16 @@
         <v>1.4055</v>
       </c>
       <c r="F42" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.1514</v>
       </c>
     </row>
     <row r="43">
@@ -2011,13 +2167,16 @@
         <v>1.4055</v>
       </c>
       <c r="F43" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.1546</v>
       </c>
     </row>
     <row r="44">
@@ -2037,13 +2196,16 @@
         <v>1.4055</v>
       </c>
       <c r="F44" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.1546</v>
       </c>
     </row>
     <row r="45">
@@ -2063,13 +2225,16 @@
         <v>1.4055</v>
       </c>
       <c r="F45" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.1546</v>
       </c>
     </row>
     <row r="46">
@@ -2089,13 +2254,16 @@
         <v>1.4055</v>
       </c>
       <c r="F46" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.1546</v>
       </c>
     </row>
     <row r="47">
@@ -2115,13 +2283,16 @@
         <v>1.4055</v>
       </c>
       <c r="F47" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.1546</v>
       </c>
     </row>
     <row r="48">
@@ -2141,13 +2312,16 @@
         <v>1.5386</v>
       </c>
       <c r="F48" t="n">
+        <v>1.6604</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1.6604</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.1546</v>
       </c>
     </row>
     <row r="49">
@@ -2167,13 +2341,16 @@
         <v>1.6729</v>
       </c>
       <c r="F49" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1556</v>
       </c>
     </row>
     <row r="50">
@@ -2193,13 +2370,16 @@
         <v>1.7779</v>
       </c>
       <c r="F50" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.1556</v>
       </c>
     </row>
     <row r="51">
@@ -2219,13 +2399,16 @@
         <v>1.8289</v>
       </c>
       <c r="F51" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.1556</v>
       </c>
     </row>
     <row r="52">
@@ -2245,13 +2428,16 @@
         <v>1.8629</v>
       </c>
       <c r="F52" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="53">
@@ -2271,13 +2457,16 @@
         <v>1.8981</v>
       </c>
       <c r="F53" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="54">
@@ -2297,13 +2486,16 @@
         <v>1.9591</v>
       </c>
       <c r="F54" t="n">
+        <v>1.5869</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1.5869</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="55">
@@ -2323,13 +2515,16 @@
         <v>1.9691</v>
       </c>
       <c r="F55" t="n">
+        <v>1.5869</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1.5869</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="56">
@@ -2349,13 +2544,16 @@
         <v>2.0631</v>
       </c>
       <c r="F56" t="n">
+        <v>1.5574</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1.5574</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="57">
@@ -2375,13 +2573,16 @@
         <v>2.2581</v>
       </c>
       <c r="F57" t="n">
+        <v>1.5574</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1.5574</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="58">
@@ -2401,13 +2602,16 @@
         <v>2.2611</v>
       </c>
       <c r="F58" t="n">
+        <v>1.5574</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1.5574</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.1926</v>
       </c>
     </row>
     <row r="59">
@@ -2427,13 +2631,16 @@
         <v>2.2661</v>
       </c>
       <c r="F59" t="n">
+        <v>1.5574</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.5574</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.1956</v>
       </c>
     </row>
     <row r="60">
@@ -2453,13 +2660,16 @@
         <v>2.3061</v>
       </c>
       <c r="F60" t="n">
+        <v>1.5574</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1.5574</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.1956</v>
       </c>
     </row>
     <row r="61">
@@ -2479,13 +2689,16 @@
         <v>2.4638</v>
       </c>
       <c r="F61" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.1956</v>
       </c>
     </row>
     <row r="62">
@@ -2505,13 +2718,16 @@
         <v>2.4666</v>
       </c>
       <c r="F62" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.1956</v>
       </c>
     </row>
     <row r="63">
@@ -2531,13 +2747,16 @@
         <v>2.4746</v>
       </c>
       <c r="F63" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.197</v>
       </c>
     </row>
     <row r="64">
@@ -2557,13 +2776,16 @@
         <v>2.4746</v>
       </c>
       <c r="F64" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.197</v>
       </c>
     </row>
     <row r="65">
@@ -2583,13 +2805,16 @@
         <v>2.4746</v>
       </c>
       <c r="F65" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.197</v>
       </c>
     </row>
     <row r="66">
@@ -2609,13 +2834,16 @@
         <v>2.6746</v>
       </c>
       <c r="F66" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="67">
@@ -2635,13 +2863,16 @@
         <v>3.1527</v>
       </c>
       <c r="F67" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="68">
@@ -2661,13 +2892,16 @@
         <v>3.2407</v>
       </c>
       <c r="F68" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="69">
@@ -2687,13 +2921,16 @@
         <v>3.016</v>
       </c>
       <c r="F69" t="n">
+        <v>1.5424</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>1.755</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1.5424</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.199</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/argentina_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/argentina_power_capacity.xlsx
@@ -26,8 +26,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -67,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -823,7 +824,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -838,7 +838,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -853,7 +852,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -882,7 +880,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -962,7 +959,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -991,7 +988,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1020,7 +1017,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1049,7 +1046,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1078,7 +1075,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1107,7 +1104,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1136,7 +1133,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1165,7 +1162,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1194,7 +1191,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1223,7 +1220,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1252,7 +1249,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1281,7 +1278,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1310,7 +1307,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1339,7 +1336,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1368,7 +1365,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1397,7 +1394,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1426,7 +1423,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1455,7 +1452,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1484,7 +1481,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1513,7 +1510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1542,7 +1539,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1571,7 +1568,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1600,7 +1597,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1629,7 +1626,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1658,7 +1655,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1687,7 +1684,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1716,7 +1713,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1745,7 +1742,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1774,7 +1771,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1803,7 +1800,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1832,7 +1829,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1861,7 +1858,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1890,7 +1887,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1919,7 +1916,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1948,7 +1945,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1977,7 +1974,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2006,7 +2003,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2035,7 +2032,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2064,7 +2061,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2093,7 +2090,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2122,7 +2119,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2151,7 +2148,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2180,7 +2177,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2209,7 +2206,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2238,7 +2235,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2267,7 +2264,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2296,7 +2293,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2325,7 +2322,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2354,7 +2351,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2383,7 +2380,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2412,7 +2409,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2441,7 +2438,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2470,7 +2467,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2499,7 +2496,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2528,7 +2525,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2557,7 +2554,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2586,7 +2583,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2615,7 +2612,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2644,7 +2641,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2673,7 +2670,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2702,7 +2699,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2731,7 +2728,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2760,7 +2757,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2789,7 +2786,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2818,7 +2815,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2847,7 +2844,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2876,7 +2873,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2905,7 +2902,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">

--- a/output/Data and Chart Outputs/argentina_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/argentina_power_capacity.xlsx
@@ -162,6 +162,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Argentina installed generation capacity (CAMMESA) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -295,7 +296,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -323,7 +324,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -351,7 +352,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -379,7 +380,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
